--- a/artfynd/A 33153-2024 artfynd.xlsx
+++ b/artfynd/A 33153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96365907</v>
+        <v>96365715</v>
       </c>
       <c r="B2" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724640.7797349566</v>
+        <v>724620</v>
       </c>
       <c r="R2" t="n">
-        <v>6378821.195020546</v>
+        <v>6378948</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,27 +747,18 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,39 +781,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96350190</v>
+        <v>96365104</v>
       </c>
       <c r="B3" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -834,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724454.9121589113</v>
+        <v>724713</v>
       </c>
       <c r="R3" t="n">
-        <v>6378855.086924425</v>
+        <v>6378985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,39 +879,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96365499</v>
+        <v>96366043</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -951,13 +911,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724586.5534946556</v>
+        <v>724823</v>
       </c>
       <c r="R4" t="n">
-        <v>6379001.833724188</v>
+        <v>6378753</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,19 +944,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96365658</v>
+        <v>96350280</v>
       </c>
       <c r="B5" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724592.0611406355</v>
+        <v>724399</v>
       </c>
       <c r="R5" t="n">
-        <v>6378950.979538889</v>
+        <v>6378879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96365673</v>
+        <v>96365658</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,13 +1115,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724593.2556368849</v>
+        <v>724592</v>
       </c>
       <c r="R6" t="n">
-        <v>6378948.891482745</v>
+        <v>6378951</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,19 +1148,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96365715</v>
+        <v>96365709</v>
       </c>
       <c r="B7" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,38 +1192,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>174</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724620.2702980095</v>
+        <v>724620</v>
       </c>
       <c r="R7" t="n">
-        <v>6378948.230171504</v>
+        <v>6378948</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,19 +1250,14 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,7 +1266,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,15 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96365701</v>
+        <v>96365906</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,36 +1299,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724620.2702980095</v>
+        <v>724641</v>
       </c>
       <c r="R8" t="n">
-        <v>6378948.230171504</v>
+        <v>6378821</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,24 +1357,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,37 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96365906</v>
+        <v>96350278</v>
       </c>
       <c r="B9" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>3286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,13 +1426,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724640.7797349566</v>
+        <v>724399</v>
       </c>
       <c r="R9" t="n">
-        <v>6378821.195020546</v>
+        <v>6378879</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,22 +1456,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,15 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96365709</v>
+        <v>96366256</v>
       </c>
       <c r="B10" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,23 +1503,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>3624</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1663,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724620.2702980095</v>
+        <v>724766</v>
       </c>
       <c r="R10" t="n">
-        <v>6378948.230171504</v>
+        <v>6378869</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1696,24 +1557,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,37 +1590,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96366256</v>
+        <v>96364812</v>
       </c>
       <c r="B11" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3624</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1626,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724766.0145056866</v>
+        <v>724786</v>
       </c>
       <c r="R11" t="n">
-        <v>6378869.046092108</v>
+        <v>6378888</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,19 +1659,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,15 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96350064</v>
+        <v>96364882</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,33 +1703,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3712</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1911,13 +1728,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724448.9942476699</v>
+        <v>724784</v>
       </c>
       <c r="R12" t="n">
-        <v>6378786.367039279</v>
+        <v>6378886</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1941,22 +1758,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,15 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96365745</v>
+        <v>96365673</v>
       </c>
       <c r="B13" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,21 +1805,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2028,13 +1830,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724640.1139962259</v>
+        <v>724593</v>
       </c>
       <c r="R13" t="n">
-        <v>6378950.403817078</v>
+        <v>6378949</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,19 +1863,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,15 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96365904</v>
+        <v>96365745</v>
       </c>
       <c r="B14" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +1921,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724640.7797349566</v>
+        <v>724640</v>
       </c>
       <c r="R14" t="n">
-        <v>6378821.195020546</v>
+        <v>6378950</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2178,19 +1965,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,15 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103391178</v>
+        <v>96365904</v>
       </c>
       <c r="B15" t="n">
-        <v>96225</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,41 +2009,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Anga Bendes, Gtl</t>
+          <t>Bendes, Anga, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724526.5039634357</v>
+        <v>724641</v>
       </c>
       <c r="R15" t="n">
-        <v>6378828.883200066</v>
+        <v>6378821</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,22 +2064,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,22 +2078,956 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103391178</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99010</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Anga Bendes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>724527</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6378829</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Cecilia Nygren</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Cecilia Nygren, Annika Forsslund</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>96364883</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>724784</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6378886</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera ex i området</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96365701</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>724620</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6378948</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera i området</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103391135</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Anga bendes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>724497</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6378753</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96365907</v>
+      </c>
+      <c r="B20" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>724641</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6378821</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96364880</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>724784</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6378886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96350190</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>724455</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6378855</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96364825</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>724786</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6378888</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>96365499</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bendes, Anga, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>724587</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6379002</v>
+      </c>
+      <c r="S24" t="n">
+        <v>14</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33153-2024 artfynd.xlsx
+++ b/artfynd/A 33153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96366043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96350280</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96350278</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96366256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96364812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96364882</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365745</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365904</t>
         </is>
       </c>
     </row>
@@ -2199,6 +2274,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103391178</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96364883</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365701</t>
         </is>
       </c>
     </row>
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103391135</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365907</t>
         </is>
       </c>
     </row>
@@ -2722,6 +2822,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96364880</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2824,6 +2929,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96350190</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96364825</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,8 +3143,38 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96365499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>